--- a/outputs/per-fund/vc-investments-multicoin-capital.xlsx
+++ b/outputs/per-fund/vc-investments-multicoin-capital.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Multicoin Capital. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Multicoin Capital. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -22288,11 +22288,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>coinfund, dragonfly, multicoin-capital</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -22534,11 +22534,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, polychain</t>
+          <t>1kx, blockchain-capital, huobi-ventures, multicoin-capital, polychain, sequoia-capital</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -22652,11 +22652,11 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>galaxy-digital, hack-vc, multicoin-capital</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -22715,11 +22715,11 @@
         <v>2</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures</t>
+          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -22774,11 +22774,11 @@
         <v>2</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, pantera, paradigm</t>
+          <t>multicoin-capital, pantera, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -22900,11 +22900,11 @@
         <v>1</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>galaxy-digital, multicoin-capital</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -23026,11 +23026,11 @@
         <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, multicoin-capital</t>
+          <t>coinbase-ventures, multicoin-capital, yzi-labs</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -23274,11 +23274,11 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>arrington-capital, hashed, hashkey-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -23522,11 +23522,11 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>huobi-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -23585,11 +23585,11 @@
         <v>5</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, lemniscap, multicoin-capital</t>
+          <t>coinbase-ventures, digital-currency-group, lemniscap, multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -23711,11 +23711,11 @@
         <v>1</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, cms-holdings, multicoin-capital</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -23774,11 +23774,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>coinbase-ventures, digital-currency-group, dragonfly, hashed, multicoin-capital</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -23898,11 +23898,11 @@
         <v>2</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -24024,11 +24024,11 @@
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, multicoin-capital</t>
+          <t>cms-holdings, electric-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -24150,11 +24150,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>1kx, multicoin-capital, sevenx-ventures</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -24213,11 +24213,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, polychain</t>
+          <t>alameda-research, hypersphere, multicoin-capital, polychain</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -24274,11 +24274,11 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, cms-holdings, multicoin-capital</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -24337,11 +24337,11 @@
         <v>1</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>cms-holdings, multicoin-capital</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -24400,11 +24400,11 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -24463,11 +24463,11 @@
         <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>coinfund, multicoin-capital</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -24526,11 +24526,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>hashed, multicoin-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -24585,11 +24585,11 @@
         <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, polychain</t>
+          <t>multicoin-capital, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -24768,11 +24768,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, hashkey-capital, mechanism-capital, multicoin-capital, solana-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -24827,11 +24827,11 @@
         <v>5</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>animoca-brands, animoca-brands-japan, iosg-ventures, multicoin-capital, spartan-group</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -24890,11 +24890,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>coinfund, multicoin-capital</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -24949,11 +24949,11 @@
         <v>2</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, alliance-dao, delphi-ventures, fenbushi-capital, iosg-ventures, multicoin-capital, okx-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -25067,11 +25067,11 @@
         <v>2</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, multicoin-capital, polychain</t>
+          <t>a16z-crypto, alameda-research, cms-holdings, multicoin-capital, polychain</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -25130,11 +25130,11 @@
         <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>coinfund, multicoin-capital</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -25191,11 +25191,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, multicoin-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -25254,11 +25254,11 @@
         <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, semantic-ventures</t>
+          <t>alliance-dao, delphi-ventures, multicoin-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -25317,11 +25317,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, multicoin-capital, paradigm</t>
+          <t>circle-ventures, coinbase-ventures, multicoin-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -25439,11 +25439,11 @@
         <v>1</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, multicoin-capital</t>
+          <t>a16z-crypto, alameda-research, multicoin-capital</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -25561,11 +25561,11 @@
         <v>0</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, galaxy-digital, multicoin-capital</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -25624,11 +25624,11 @@
         <v>0</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, cms-holdings, multicoin-capital</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -25687,11 +25687,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, gsr, multicoin-capital</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -25750,11 +25750,11 @@
         <v>1</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11, multicoin-capital</t>
+          <t>blockchain-capital, cmt-digital, framework-ventures, maven11, multicoin-capital</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -25813,11 +25813,11 @@
         <v>2</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>delphi-ventures, hypersphere, multicoin-capital, robot-ventures, spartan-group, yzi-labs</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -25876,11 +25876,11 @@
         <v>1</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>longhash-ventures, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25937,11 +25937,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, multicoin-capital</t>
+          <t>a16z-crypto, coinbase-ventures, coinfund, digital-currency-group, hashed, hypersphere, multicoin-capital</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -25996,11 +25996,11 @@
         <v>1</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, sequoia-capital</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -26057,11 +26057,11 @@
         <v>1</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>mechanism-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -26120,11 +26120,11 @@
         <v>1</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -26183,11 +26183,11 @@
         <v>0</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>cmt-digital, fenbushi-capital, iosg-ventures, multicoin-capital, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -26246,11 +26246,11 @@
         <v>1</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>alameda-research, animoca-brands, animoca-brands-japan, dragonfly, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -26305,11 +26305,11 @@
         <v>1</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, gsr, multicoin-capital, parafi-capital, sequoia-capital, spartan-group</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -26368,11 +26368,11 @@
         <v>0</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>animoca-brands, hashed, multicoin-capital</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -26431,11 +26431,11 @@
         <v>0</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>alameda-research, hack-vc, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -26547,11 +26547,11 @@
         <v>1</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital, sfermion, solana-ventures</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -26606,11 +26606,11 @@
         <v>0</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital, sfermion</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -26669,11 +26669,11 @@
         <v>2</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, multicoin-capital</t>
+          <t>alameda-research, electric-capital, multicoin-capital, sequoia-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -26732,11 +26732,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, sequoia-capital</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -26791,11 +26791,11 @@
         <v>2</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>alameda-research, animoca-brands, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -26854,11 +26854,11 @@
         <v>0</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>alameda-research, cmt-digital, coinbase-ventures, coinfund, dragonfly, hashed, hashkey-capital, iosg-ventures, multicoin-capital, parafi-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -26917,11 +26917,11 @@
         <v>1</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, multicoin-capital</t>
+          <t>alameda-research, alliance-dao, animoca-brands, figment-capital, hashkey-capital, huobi-ventures, mechanism-capital, multicoin-capital, polygon-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -26980,11 +26980,11 @@
         <v>2</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, animoca-brands, jump-crypto, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -27106,11 +27106,11 @@
         <v>2</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, hashkey-capital, mirana-ventures, multicoin-capital, sfermion, solana-ventures, spartan-group, yzi-labs</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -27295,11 +27295,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -27358,11 +27358,11 @@
         <v>0</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, multicoin-capital</t>
+          <t>animoca-brands, coinbase-ventures, coinfund, digital-currency-group, figment-capital, hashed, jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -27421,11 +27421,11 @@
         <v>1</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -27543,11 +27543,11 @@
         <v>0</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>amber-group, multicoin-capital</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -27602,11 +27602,11 @@
         <v>0</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>amber-group, multicoin-capital</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -27665,11 +27665,11 @@
         <v>0</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, pantera</t>
+          <t>multicoin-capital, pantera, solana-ventures</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -27787,11 +27787,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -27850,11 +27850,11 @@
         <v>0</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, multicoin-capital</t>
+          <t>a16z-crypto, coinbase-ventures, hashed, multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -27913,11 +27913,11 @@
         <v>1</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>digital-currency-group, multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -28102,11 +28102,11 @@
         <v>3</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, multicoin-capital</t>
+          <t>a16z-crypto, animoca-brands, coinbase-ventures, coinfund, hypersphere, multicoin-capital, polygon-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -28165,11 +28165,11 @@
         <v>0</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>animoca-brands, coinfund, hashed, multicoin-capital, yzi-labs</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -28228,11 +28228,11 @@
         <v>2</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, multicoin-capital, paradigm</t>
+          <t>a16z-crypto, animoca-brands, coinbase-ventures, multicoin-capital, paradigm, solana-ventures</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -28291,11 +28291,11 @@
         <v>1</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
@@ -28354,11 +28354,11 @@
         <v>1</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>alameda-research, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -28417,11 +28417,11 @@
         <v>0</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, multicoin-capital</t>
+          <t>blockchain-capital, framework-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -28480,11 +28480,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>iosg-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -28665,11 +28665,11 @@
         <v>0</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>gsr, multicoin-capital</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -28791,11 +28791,11 @@
         <v>0</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, multicoin-capital</t>
+          <t>a16z-crypto, alameda-research, circle-ventures, jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -28854,11 +28854,11 @@
         <v>0</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, delphi-ventures, framework-ventures, multicoin-capital, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -28917,11 +28917,11 @@
         <v>0</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, multicoin-capital</t>
+          <t>framework-ventures, hashed, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
@@ -28980,11 +28980,11 @@
         <v>0</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -29045,11 +29045,11 @@
         <v>1</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, multicoin-capital</t>
+          <t>coinbase-ventures, delphi-ventures, gsr, hypersphere, multicoin-capital</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -29108,11 +29108,11 @@
         <v>1</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>alliance-dao, cms-holdings, delphi-ventures, digital-currency-group, mechanism-capital, multicoin-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -29171,11 +29171,11 @@
         <v>2</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -29234,11 +29234,11 @@
         <v>0</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -29297,11 +29297,11 @@
         <v>0</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, multicoin-capital</t>
+          <t>circle-ventures, lemniscap, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -29360,11 +29360,11 @@
         <v>3</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>circle-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M116" s="7" t="inlineStr">
@@ -29482,11 +29482,11 @@
         <v>0</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>dragonfly, multicoin-capital, polygon-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
@@ -29545,11 +29545,11 @@
         <v>0</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, polygon-ventures</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
@@ -29671,11 +29671,11 @@
         <v>2</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>big-brain-holdings, circle-ventures, multicoin-capital, sequoia-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
@@ -29734,11 +29734,11 @@
         <v>1</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>cmt-digital, multicoin-capital, sfermion</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
@@ -29799,11 +29799,11 @@
         <v>0</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>foresight-ventures, hypersphere, jump-crypto, mh-ventures, multicoin-capital, okx-ventures</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
@@ -29862,11 +29862,11 @@
         <v>1</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>coinfund, multicoin-capital</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
@@ -29925,11 +29925,11 @@
         <v>1</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, multicoin-capital, polygon-ventures</t>
         </is>
       </c>
       <c r="M125" s="10" t="n"/>
@@ -29984,11 +29984,11 @@
         <v>2</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, robot-ventures</t>
+          <t>hack-vc, multicoin-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M126" s="7" t="inlineStr">
@@ -30047,11 +30047,11 @@
         <v>1</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, jump-crypto, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
@@ -30108,11 +30108,11 @@
         <v>0</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, multicoin-capital</t>
+          <t>arrington-capital, borderless-capital, coinbase-ventures, multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
@@ -30169,11 +30169,11 @@
         <v>0</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>borderless-capital, cmt-digital, delphi-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr">
@@ -30232,11 +30232,11 @@
         <v>1</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>big-brain-holdings, fenbushi-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
@@ -30291,11 +30291,11 @@
         <v>1</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>circle-ventures, iosg-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr">
@@ -30354,11 +30354,11 @@
         <v>1</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>animoca-brands, delphi-ventures, foresight-ventures, hack-vc, longhash-ventures, mh-ventures, multicoin-capital, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
@@ -30480,11 +30480,11 @@
         <v>0</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, multicoin-capital</t>
+          <t>animoca-brands, arrington-capital, figment-capital, mechanism-capital, mh-ventures, multicoin-capital, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -30543,11 +30543,11 @@
         <v>1</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, pantera</t>
+          <t>hack-vc, multicoin-capital, pantera, parafi-capital</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr">
@@ -30606,11 +30606,11 @@
         <v>1</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -30669,11 +30669,11 @@
         <v>1</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>big-brain-holdings, cms-holdings, multicoin-capital, okx-ventures</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -30795,11 +30795,11 @@
         <v>1</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, multicoin-capital</t>
+          <t>borderless-capital, coinbase-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -30917,11 +30917,11 @@
         <v>1</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, robot-ventures</t>
+          <t>multicoin-capital, okx-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M141" s="7" t="inlineStr">
@@ -31033,11 +31033,11 @@
         <v>0</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, pantera</t>
+          <t>multicoin-capital, pantera, sequoia-capital</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -31096,11 +31096,11 @@
         <v>1</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>blockchain-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -31155,11 +31155,11 @@
         <v>0</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>iosg-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M145" s="7" t="inlineStr">
@@ -31218,11 +31218,11 @@
         <v>1</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>borderless-capital, gsr, hypersphere, multicoin-capital</t>
         </is>
       </c>
       <c r="M146" s="7" t="inlineStr">
@@ -31281,11 +31281,11 @@
         <v>1</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, parafi-capital</t>
         </is>
       </c>
       <c r="M147" s="7" t="inlineStr">
@@ -31342,11 +31342,11 @@
         <v>2</v>
       </c>
       <c r="K148" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, multicoin-capital</t>
+          <t>borderless-capital, delphi-ventures, dragonfly, gsr, mh-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M148" s="7" t="inlineStr">
@@ -31594,11 +31594,11 @@
         <v>1</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, paradigm</t>
+          <t>multicoin-capital, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31779,11 +31779,11 @@
         <v>2</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>galaxy-digital, gsr, multicoin-capital</t>
         </is>
       </c>
       <c r="M155" s="7" t="inlineStr">
@@ -31842,11 +31842,11 @@
         <v>2</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>mechanism-capital, multicoin-capital</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -31905,11 +31905,11 @@
         <v>0</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>coinfund, multicoin-capital</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -32033,11 +32033,11 @@
         <v>1</v>
       </c>
       <c r="K159" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital</t>
+          <t>multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr">
@@ -39366,19 +39366,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
